--- a/AKC_FuerzaFIG.xlsx
+++ b/AKC_FuerzaFIG.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>Tipo</t>
   </si>
@@ -65,10 +65,10 @@
     <t>Pecho</t>
   </si>
   <si>
-    <t>Remo unilateral</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/KuDDNb7djxU?si=O9W2w9YuR91dwUfn</t>
+    <t>Remo sentado en polea</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/fPbfYDgzIgA</t>
   </si>
   <si>
     <t>Espalda</t>
@@ -98,10 +98,10 @@
     <t>https://www.youtube.com/shorts/Nwy7FD4sAFw</t>
   </si>
   <si>
-    <t>Curl inclinado con mancuernas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/hSYwo7tewik?si=uYExKxxke7YanqjQ</t>
+    <t>Curl de bíceps en polea</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/kmSnKiqvSYo</t>
   </si>
   <si>
     <t>Bíceps</t>
@@ -164,16 +164,22 @@
     <t>Piernas</t>
   </si>
   <si>
-    <t>Press inclinado con barra</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/98HWfiRonkE?si=qxqk4zpOk4DTU47Y</t>
-  </si>
-  <si>
-    <t>Curl de bíceps con mancuernas</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/MKWBV29S6c0?si=NxHxQOSIcjH4Zi9d</t>
+    <t>Straight Arm Pulldown en polea</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/dEty-WKfxV8</t>
+  </si>
+  <si>
+    <t>Dorsal/Espalda</t>
+  </si>
+  <si>
+    <t>Extensión de tríceps en polea alta</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/rTNKeT6fde8</t>
+  </si>
+  <si>
+    <t>Tríceps</t>
   </si>
   <si>
     <t>Face pull-ups en anillos</t>
@@ -212,10 +218,10 @@
     <t>Espalda/Bíceps</t>
   </si>
   <si>
-    <t>Sentadilla curtsy con mancuerna</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/O5d5-AWl8rw?si=H5y8sMaVlG9doVC2</t>
+    <t>Cable Kickback con tobillera</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/5iXaaPuR2ko</t>
   </si>
   <si>
     <t>Fondos en anillos con soporte</t>
@@ -239,13 +245,10 @@
     <t>Core/Espalda</t>
   </si>
   <si>
-    <t>Farmer Carry con Trap Bar</t>
-  </si>
-  <si>
-    <t>https://youtube.com/shorts/JmHEtZ6rwFU?si=tJxW3BXYhmJ0otlz</t>
-  </si>
-  <si>
-    <t>Cuerpo completo</t>
+    <t>Face Pull en polea</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/mWaKyzkzlSw</t>
   </si>
 </sst>
 </file>
@@ -304,19 +307,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -619,13 +620,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.02734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.890625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.046875" customWidth="1"/>
+    <col min="5" max="5" width="9.953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -880,7 +881,7 @@
         <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -891,13 +892,13 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -908,13 +909,13 @@
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -922,13 +923,13 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -939,16 +940,16 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -956,16 +957,16 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -973,16 +974,16 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -990,13 +991,13 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
         <v>26</v>
@@ -1007,13 +1008,13 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -1024,16 +1025,16 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1041,45 +1042,45 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{E8F956A3-F9D7-3C42-AD9A-D4C9A325C972}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{238FE3AA-7AEE-444A-953D-9EFABE494DBE}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{F921EDC3-B6A6-7C49-A682-739D1C858870}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{0F1031E9-0CBF-9744-A35A-AE16F61A1154}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{29363D29-0CFE-A740-B6A0-6C9D87A5595D}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{7F8FE282-FF98-644B-8323-B61A169C7685}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{E75B591D-C436-DE4C-9655-88E6D51199FA}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{5B1BCFEE-6522-4A44-A55B-0AC0915FBF95}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{6DC80506-2547-BA48-964A-AB3BBC4F9F4F}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{355A62D7-9141-FE41-9C6C-E445F807027B}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{50B3A672-39D8-DF4F-A658-E96CAEBF697F}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{133C658E-9792-1E41-B155-459ADBA205E1}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{1606E1AD-DE5B-6F42-9099-CDDD4FAFECF5}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{C58DB60F-23B3-4D48-AE37-8DB5337D0885}"/>
-    <hyperlink ref="D15" r:id="rId15" xr:uid="{5C68D6C8-716F-0A49-868F-92DABC386CCD}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{5EEDB863-6D12-354A-A774-4280BB061CC0}"/>
-    <hyperlink ref="D18" r:id="rId17" xr:uid="{255BD0AB-9E1A-BD4D-8161-541C58372D2D}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{6023E270-4613-7140-8313-D2062879B3F6}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{C1FE89E5-C0F5-3945-AEEF-95176F27FBEA}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{22DB68D9-1936-EA47-9BA2-D0FFF1D1294F}"/>
-    <hyperlink ref="D22" r:id="rId21" xr:uid="{5BC8B0A8-20FC-7142-9935-8F9F97E22D15}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{F13F1EC8-0CE4-B44D-AC95-79D099044A45}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{D0083E4C-9542-294C-96C3-CCC8312A5756}"/>
-    <hyperlink ref="D25" r:id="rId24" xr:uid="{4B7A250D-853A-1E4F-98B0-99907D622BFE}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{2AE69C50-19A8-D34C-A64A-A294EF5E538E}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{B3587FA0-1332-F645-B426-DEA8EA9E7A67}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{60C46D38-12E9-B744-A0DB-183DCC92E4B7}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{842E5564-2A1D-E148-93E6-234C42C54157}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{AA0F7C4B-2EC9-7147-9394-32389C282D22}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{E0BE8AEB-DC76-734D-92ED-60B2CC46C16E}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{1DEF4025-FBAE-F048-A041-E5F39A9B629F}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{B1FCE4DA-348D-6F40-9353-3B169E45264F}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{24740F12-6D24-1D4C-877B-3948E11FBE3E}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{2CA55D2A-301F-214F-975D-C469D01C0698}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{95E0B45B-52EA-BF45-8DAD-E8CA390AD373}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{21E4AA37-F10A-B54A-8472-424541E5033C}"/>
+    <hyperlink ref="D14" r:id="rId13" xr:uid="{F4AC9247-BCCD-534F-BE3E-2B1AA8F6801C}"/>
+    <hyperlink ref="D15" r:id="rId14" xr:uid="{46AE06EF-9913-D647-94D0-B8BBB536A834}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{86B340BD-8F57-8547-8EC2-3A4B1453CC05}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{5FE17A79-BD40-BF42-8C0C-20B569D819CB}"/>
+    <hyperlink ref="D18" r:id="rId17" xr:uid="{7D9452DF-49DF-6443-A181-1715D936178B}"/>
+    <hyperlink ref="D19" r:id="rId18" xr:uid="{05983AAD-184A-7D49-81E0-6B477AF04414}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{8D47FFDC-AB11-1D4A-813F-AD47A5145C5F}"/>
+    <hyperlink ref="D21" r:id="rId20" xr:uid="{EAB23A6F-D788-A543-96B9-BC517E1D86F5}"/>
+    <hyperlink ref="D22" r:id="rId21" xr:uid="{213AC0BD-C6FB-5844-8410-C1042F280218}"/>
+    <hyperlink ref="D23" r:id="rId22" xr:uid="{5AAFF662-E9D8-B84D-B703-3CD09068C5E0}"/>
+    <hyperlink ref="D24" r:id="rId23" xr:uid="{F2EE7F90-3C4C-2C4C-A0CD-CB3133A09BFC}"/>
+    <hyperlink ref="D25" r:id="rId24" xr:uid="{37CBA45F-2DCE-B54B-90F5-EBC5CD2FA247}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
